--- a/testcase.xlsx
+++ b/testcase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amelk\SauceDemo-Manual-QA-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7742E15D-9524-406D-BB90-5BBC41653599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B33CB9C-AB93-436C-937C-96AEF5A58161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{7736F62C-BF55-455E-BFF9-257D87FB2433}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7736F62C-BF55-455E-BFF9-257D87FB2433}"/>
   </bookViews>
   <sheets>
     <sheet name="testcase" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="69">
   <si>
     <t>Test Case</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>TC-005</t>
-  </si>
-  <si>
-    <t>complete checkout with valid information</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click checkout 
@@ -140,6 +137,108 @@
 2. Enter password
 3. Click login
  </t>
+  </si>
+  <si>
+    <t>TC-006</t>
+  </si>
+  <si>
+    <t>TC-007</t>
+  </si>
+  <si>
+    <t>TC-008</t>
+  </si>
+  <si>
+    <t>TC-009</t>
+  </si>
+  <si>
+    <t>1. Enter login
+2. Enter invalid  password
+3. Click login</t>
+  </si>
+  <si>
+    <t>Complete checkout with valid information</t>
+  </si>
+  <si>
+    <t>Checkout with empty required fields</t>
+  </si>
+  <si>
+    <t>User is logged in and has at least one product in the cart</t>
+  </si>
+  <si>
+    <t>Checkout does not proceed and a validation error is displayed</t>
+  </si>
+  <si>
+    <t>User is logged in, cart contains a product, checkout information page is open</t>
+  </si>
+  <si>
+    <t>User is logged in and on the Products page</t>
+  </si>
+  <si>
+    <t>TC-010</t>
+  </si>
+  <si>
+    <t>TC-011</t>
+  </si>
+  <si>
+    <t>Logout from application</t>
+  </si>
+  <si>
+    <t>User is logged in</t>
+  </si>
+  <si>
+    <t>Add multiple products to cart</t>
+  </si>
+  <si>
+    <t>1. Add first product to cart 
+2. Add second product to cart 
+3. Check cart badge 4. Open cart</t>
+  </si>
+  <si>
+    <t>1. Open the menu 
+2. Click Logout</t>
+  </si>
+  <si>
+    <t>Cart badge shows 2 and both selected products are displayed in the cart</t>
+  </si>
+  <si>
+    <t>User is logged out and redirected to the login page</t>
+  </si>
+  <si>
+    <t>1. Open cart 2. Click Checkout 
+3. Leave First Name, Last Name, and Postal Code empty 4. Click Pay now</t>
+  </si>
+  <si>
+    <t>Checkout did not proceed and a validation error is displayed</t>
+  </si>
+  <si>
+    <t>Checkout with missing city</t>
+  </si>
+  <si>
+    <t>1. Enter valid First Name 2. Enter valid Last Name 3. Leave City  empty 4. Click Pay now</t>
+  </si>
+  <si>
+    <t>Checkout does not proceed and an error indicating that City is required is displayed</t>
+  </si>
+  <si>
+    <t>Checkout did not proceed and an error indicating that City is required is displayed</t>
+  </si>
+  <si>
+    <t>Open product details page</t>
+  </si>
+  <si>
+    <t>1. Click a product name or image</t>
+  </si>
+  <si>
+    <t>Product details page opens and shows the correct product information.</t>
+  </si>
+  <si>
+    <t>Product details page opened and showed the correct product information.</t>
+  </si>
+  <si>
+    <t>Cart badge showed 2 and both selected products were displayed in the cart</t>
+  </si>
+  <si>
+    <t>User was logged out and redirected to the login page</t>
   </si>
 </sst>
 </file>
@@ -724,15 +823,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -908,6 +998,15 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -923,17 +1022,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3718ED29-8D0E-4332-BFD9-5DEFF1A64B02}" name="Таблица1" displayName="Таблица1" ref="A1:H7" totalsRowShown="0" dataDxfId="0">
-  <autoFilter ref="A1:H7" xr:uid="{3718ED29-8D0E-4332-BFD9-5DEFF1A64B02}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3718ED29-8D0E-4332-BFD9-5DEFF1A64B02}" name="Таблица1" displayName="Таблица1" ref="A1:H12" totalsRowShown="0" dataDxfId="8">
+  <autoFilter ref="A1:H12" xr:uid="{3718ED29-8D0E-4332-BFD9-5DEFF1A64B02}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{7042FE4C-93EF-4D50-B811-8485C2EF0386}" name="Test Case" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{B10ABD99-7C5D-489A-81CE-D5B2946BF51B}" name="ID" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{958231F2-F85B-4B67-8367-BC00EDAF3B58}" name="Title" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{D4855EEF-67F7-4E94-84FC-7FDAD183E26C}" name="Preconditions" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{DFEBA09D-C6B2-40E0-B1DB-792C554BDCE8}" name="Steps" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{DA69DCFB-D5D8-43B2-8E29-975E6EBA6FB6}" name="Expected Result" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{195B77CF-77DC-434C-A890-046ECB2530BC}" name="Actual Result" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{DE5461F1-DFFD-48ED-9361-1E51119056A1}" name="Status" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{7042FE4C-93EF-4D50-B811-8485C2EF0386}" name="Test Case" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{B10ABD99-7C5D-489A-81CE-D5B2946BF51B}" name="ID" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{958231F2-F85B-4B67-8367-BC00EDAF3B58}" name="Title" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{D4855EEF-67F7-4E94-84FC-7FDAD183E26C}" name="Preconditions" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{DFEBA09D-C6B2-40E0-B1DB-792C554BDCE8}" name="Steps" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{DA69DCFB-D5D8-43B2-8E29-975E6EBA6FB6}" name="Expected Result" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{195B77CF-77DC-434C-A890-046ECB2530BC}" name="Actual Result" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{DE5461F1-DFFD-48ED-9361-1E51119056A1}" name="Status" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1256,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC357D6-9D6E-4A22-A73A-0F3C4CAE36EC}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1309,19 +1408,19 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1334,12 +1433,14 @@
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="F3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>11</v>
@@ -1362,10 +1463,10 @@
         <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>18</v>
@@ -1391,7 +1492,7 @@
         <v>24</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>22</v>
@@ -1405,33 +1506,167 @@
         <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+    <row r="7" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
